--- a/CO国試data/CO_questions_2015.xlsx
+++ b/CO国試data/CO_questions_2015.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>3</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>True</t>
@@ -824,12 +821,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>運動器</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>True</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1808,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1844,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1901,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>True</t>
@@ -1937,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -1994,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2030,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2087,7 +2071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2123,15 +2106,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2180,7 +2163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2216,15 +2198,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2273,7 +2255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2309,15 +2290,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2366,7 +2347,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2402,15 +2382,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2459,7 +2439,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2495,15 +2474,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2593,15 +2572,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2650,7 +2629,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2686,15 +2664,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2743,7 +2721,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2779,15 +2756,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2877,15 +2854,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2934,7 +2911,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2970,15 +2946,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3027,7 +3003,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3063,15 +3038,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3120,7 +3095,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>True</t>
@@ -3156,15 +3130,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3213,7 +3187,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>True</t>
@@ -3249,15 +3222,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3347,15 +3320,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3404,7 +3377,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>False</t>
@@ -3440,15 +3412,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3497,7 +3469,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3533,15 +3504,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3590,7 +3561,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3626,15 +3596,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3683,7 +3653,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3719,15 +3688,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3776,7 +3745,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>True</t>
@@ -3812,15 +3780,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3869,7 +3837,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3905,15 +3872,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3962,7 +3929,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3998,15 +3964,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4055,7 +4021,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4091,15 +4056,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4148,7 +4113,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4184,15 +4148,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4241,7 +4205,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>True</t>
@@ -4277,15 +4240,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>失明予防</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4334,7 +4297,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>True</t>
@@ -4370,15 +4332,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4427,7 +4389,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4463,15 +4424,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4520,7 +4481,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4556,15 +4516,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4613,7 +4573,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4649,15 +4608,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4706,7 +4665,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4742,15 +4700,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4799,7 +4757,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4835,15 +4792,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4892,7 +4849,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4928,15 +4884,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4985,7 +4941,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5021,15 +4976,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5078,7 +5033,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5114,15 +5068,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5171,7 +5125,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5207,15 +5160,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>1</v>
       </c>
@@ -5264,7 +5217,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5300,15 +5252,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -5357,7 +5309,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>False</t>
@@ -5393,15 +5344,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5450,7 +5401,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>True</t>
@@ -5486,15 +5436,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5543,7 +5493,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>True</t>
@@ -5579,15 +5528,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5636,7 +5585,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5672,15 +5620,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5729,7 +5677,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>True</t>
@@ -5765,15 +5712,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>4</v>
       </c>
@@ -5822,7 +5769,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5858,15 +5804,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>4</v>
       </c>
@@ -5915,7 +5861,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5951,15 +5896,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>4</v>
       </c>
@@ -6049,15 +5994,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>2</v>
       </c>
@@ -6106,7 +6051,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6142,15 +6086,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6199,7 +6143,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>True</t>
@@ -6235,15 +6178,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6292,7 +6235,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>True</t>
@@ -6328,15 +6270,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -6385,7 +6327,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6421,15 +6362,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>4</v>
       </c>
@@ -6478,7 +6419,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6514,15 +6454,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6571,7 +6511,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6607,15 +6546,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6705,15 +6644,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6803,15 +6742,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6861,7 +6800,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>False</t>
@@ -6897,15 +6835,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>1</v>
       </c>
@@ -6955,7 +6893,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>False</t>
@@ -6991,15 +6928,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7089,15 +7026,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7187,15 +7124,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2</v>
       </c>
@@ -7285,15 +7222,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7383,15 +7320,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7441,7 +7378,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7477,15 +7413,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7575,15 +7511,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>感覚器</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7632,7 +7568,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>True</t>
@@ -7671,12 +7606,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>1</v>
       </c>
@@ -7725,7 +7660,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7761,15 +7695,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7818,7 +7752,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7854,15 +7787,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>感覚器</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7911,7 +7844,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7947,15 +7879,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -8004,7 +7936,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8040,15 +7971,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8097,7 +8028,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8133,15 +8063,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8190,7 +8120,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8226,15 +8155,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>臨床心理</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8283,7 +8212,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8322,12 +8250,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8376,7 +8304,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8412,15 +8339,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8469,7 +8396,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8505,15 +8431,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8562,7 +8488,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8598,15 +8523,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8655,7 +8580,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8691,15 +8615,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8748,7 +8672,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8784,15 +8707,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8841,7 +8764,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8877,15 +8799,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8934,7 +8856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8970,15 +8891,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9027,7 +8948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>True</t>
@@ -9063,15 +8983,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>4</v>
       </c>
@@ -9121,7 +9041,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>True</t>
@@ -9157,15 +9076,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9214,7 +9133,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>True</t>
@@ -9250,15 +9168,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9307,7 +9225,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9343,15 +9260,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9400,7 +9317,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9436,15 +9352,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9493,7 +9409,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9529,15 +9444,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9587,7 +9502,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9623,15 +9537,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9680,7 +9594,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9716,15 +9629,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -9774,7 +9687,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9810,15 +9722,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -9867,7 +9779,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9903,15 +9814,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>3</v>
       </c>
@@ -9960,7 +9871,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -9996,15 +9906,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10053,7 +9963,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10089,15 +9998,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10146,7 +10055,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>True</t>
@@ -10185,12 +10093,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10239,7 +10147,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>True</t>
@@ -10275,15 +10182,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10332,7 +10239,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10368,15 +10274,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10425,7 +10331,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10461,15 +10366,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10518,7 +10423,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10554,15 +10458,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10611,7 +10515,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10647,15 +10550,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10704,7 +10607,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>True</t>
@@ -10740,15 +10642,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10797,7 +10699,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10833,15 +10734,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10890,7 +10791,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>True</t>
@@ -10926,15 +10826,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10983,7 +10883,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11019,15 +10918,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11076,7 +10975,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>True</t>
@@ -11112,15 +11010,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11169,7 +11067,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>True</t>
@@ -11205,15 +11102,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11262,7 +11159,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>True</t>
@@ -11298,15 +11194,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11355,7 +11251,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>True</t>
@@ -11391,15 +11286,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11448,7 +11343,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11484,15 +11378,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11541,7 +11435,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11577,15 +11470,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11634,7 +11527,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>True</t>
@@ -11670,15 +11562,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11727,7 +11619,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11763,15 +11654,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11861,15 +11752,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11918,7 +11809,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11954,15 +11844,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>4</v>
       </c>
@@ -12011,7 +11901,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12047,15 +11936,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12104,7 +11993,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12140,15 +12028,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12197,7 +12085,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12233,15 +12120,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>1</v>
       </c>
@@ -12290,7 +12177,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12326,15 +12212,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>4</v>
       </c>
@@ -12383,7 +12269,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12419,15 +12304,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12476,7 +12361,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12512,15 +12396,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12569,7 +12453,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>True</t>
@@ -12605,15 +12488,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12662,7 +12545,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12698,15 +12580,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12755,7 +12637,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>True</t>
@@ -12791,15 +12672,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12848,7 +12729,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>False</t>
@@ -12884,15 +12764,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>4</v>
       </c>
@@ -12942,7 +12822,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>True</t>
@@ -12978,15 +12857,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -13035,7 +12914,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13071,15 +12949,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>4</v>
       </c>
@@ -13128,7 +13006,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13164,15 +13041,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>4</v>
       </c>
@@ -13221,7 +13098,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>True</t>
@@ -13257,15 +13133,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13314,7 +13190,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13350,15 +13225,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13407,7 +13282,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>True</t>
@@ -13443,15 +13317,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13500,7 +13374,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>True</t>
@@ -13536,15 +13409,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -13593,7 +13466,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>True</t>
@@ -13629,15 +13501,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13727,15 +13599,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>5</v>
       </c>
@@ -13785,7 +13657,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
       <c r="S143" t="inlineStr">
         <is>
           <t>False</t>
@@ -13821,15 +13692,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13919,15 +13790,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -14017,15 +13888,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -14075,7 +13946,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
           <t>False</t>
@@ -14111,15 +13981,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14169,7 +14039,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr"/>
       <c r="S147" t="inlineStr">
         <is>
           <t>False</t>
@@ -14205,15 +14074,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14303,15 +14172,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14401,15 +14270,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14459,7 +14328,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>False</t>
@@ -14495,15 +14363,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>4</v>
       </c>
@@ -14553,7 +14421,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
           <t>True</t>

--- a/CO国試data/CO_questions_2015.xlsx
+++ b/CO国試data/CO_questions_2015.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>運動器</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>運動器</t>
+          <t>骨、関節の構造と機能</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能検査の心理的、社会的側面についての配慮</t>
+          <t>患者、障害者への検査</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3964,12 +3964,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>失明予防</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>失明予防</t>
+          <t>予防と対策</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>ロービジョンケア</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5344,12 +5344,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5436,12 +5436,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5712,12 +5712,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5896,12 +5896,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5994,12 +5994,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能検査の心理的、社会的側面についての配慮</t>
+          <t>診療録、医療記録</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6362,12 +6362,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6454,12 +6454,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6546,12 +6546,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6644,12 +6644,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能検査の心理的、社会的側面についての配慮</t>
+          <t>患者、障害者への検査</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6928,12 +6928,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7026,12 +7026,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7320,12 +7320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>両眼視機能訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7511,12 +7511,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>感覚器</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>感覚器</t>
+          <t>視覚系の構造と機能</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>感覚器</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>感覚器</t>
+          <t>前庭平衡系の構造と機能</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7879,12 +7879,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8155,12 +8155,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正訓練の臨床心理概要</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>視能矯正訓練の臨床心理概要</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8247,12 +8247,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>瞳孔反応</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8431,12 +8431,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8615,12 +8615,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8799,12 +8799,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8891,12 +8891,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8983,12 +8983,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9076,12 +9076,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9168,12 +9168,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9352,12 +9352,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9444,12 +9444,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の投与法</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9629,12 +9629,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9722,12 +9722,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>色覚検査</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9906,12 +9906,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9998,12 +9998,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10182,12 +10182,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10366,12 +10366,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10458,12 +10458,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10734,12 +10734,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査の心理的、社会的側面についての配慮</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能検査の心理的、社会的側面についての配慮</t>
+          <t>患者、障害者への検査</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10826,12 +10826,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10918,12 +10918,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11194,12 +11194,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11286,12 +11286,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11378,12 +11378,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11470,12 +11470,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11562,12 +11562,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11936,12 +11936,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12028,12 +12028,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12120,12 +12120,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12304,12 +12304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12396,12 +12396,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12488,12 +12488,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12672,12 +12672,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能障害のリハビリテーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>視能障害のリハビリテーション</t>
+          <t>ロービジョン</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12764,12 +12764,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12857,12 +12857,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12949,12 +12949,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13041,12 +13041,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13409,12 +13409,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13501,12 +13501,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13599,12 +13599,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13692,12 +13692,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13790,12 +13790,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13888,12 +13888,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13981,12 +13981,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14074,12 +14074,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14172,12 +14172,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14270,12 +14270,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14363,12 +14363,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2015.xlsx
+++ b/CO国試data/CO_questions_2015.xlsx
@@ -550,7 +550,11 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>神経細胞、神経線維、軸索、髄鞘、神経膠細胞</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>3</v>
       </c>
@@ -642,7 +646,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +742,11 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>脳（大脳、間脳、中脳、橋、延髄、小脳）</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -826,7 +838,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +929,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1020,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -1102,7 +1111,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1207,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>染色体</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1286,7 +1303,6 @@
           <t>骨、関節の構造と機能</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1394,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1485,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -1562,7 +1576,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -1654,7 +1667,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -1746,7 +1763,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1838,7 +1859,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1930,7 +1955,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2022,7 +2051,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
@@ -2114,7 +2147,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>単眼運動とその法則</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2206,7 +2243,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2298,7 +2339,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2390,7 +2435,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>涙液層破壊時間〈BUT〉</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2482,7 +2531,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2580,7 +2633,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -2672,7 +2729,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2764,7 +2820,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2862,7 +2917,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2954,7 +3013,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3046,7 +3104,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>交感神経薬</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3138,7 +3200,11 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3230,7 +3296,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3328,7 +3398,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>倒像、直像鏡検査</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3420,7 +3494,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3512,7 +3585,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
@@ -3604,7 +3681,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3696,7 +3772,6 @@
           <t>患者、障害者への検査</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -3788,7 +3863,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>角膜形状解析、角膜トポグラフィ</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3880,7 +3959,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>近見反応</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3972,7 +4055,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4064,7 +4146,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4156,7 +4237,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>網膜色素変性、その他の変性およびジストロフィ</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4248,7 +4333,11 @@
           <t>予防と対策</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>失明（視能障害）原因疾患</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4340,7 +4429,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4432,7 +4525,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4524,7 +4616,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4616,7 +4707,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -4708,7 +4798,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4800,7 +4889,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>3</v>
       </c>
@@ -4892,7 +4980,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4984,7 +5076,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5076,7 +5167,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5168,7 +5258,6 @@
           <t>ロービジョンケア</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>1</v>
       </c>
@@ -5260,7 +5349,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -5352,7 +5440,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>合併症</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5444,7 +5536,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5536,7 +5627,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>適応と予後</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5628,7 +5723,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5720,7 +5814,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>4</v>
       </c>
@@ -5812,7 +5905,11 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>融像訓練</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>4</v>
       </c>
@@ -5904,7 +6001,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>4</v>
       </c>
@@ -6002,7 +6103,6 @@
           <t>診療録、医療記録</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>2</v>
       </c>
@@ -6094,7 +6194,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6186,7 +6285,6 @@
           <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>3</v>
       </c>
@@ -6278,7 +6376,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>斜視弱視</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -6370,7 +6472,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>4</v>
       </c>
@@ -6462,7 +6568,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6554,7 +6664,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6652,7 +6761,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6750,7 +6863,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6843,7 +6955,11 @@
           <t>患者、障害者への検査</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>小児、高齢者、障害者への対応</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
@@ -6936,7 +7052,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7034,7 +7154,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7132,7 +7251,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2</v>
       </c>
@@ -7230,7 +7348,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>4</v>
       </c>
@@ -7328,7 +7445,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7421,7 +7542,6 @@
           <t>両眼視機能訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7519,7 +7639,11 @@
           <t>視覚系の構造と機能</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>視神経、視交叉、視索、外側膝状体</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7611,7 +7735,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>1</v>
       </c>
@@ -7703,7 +7826,11 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>シナプス、神経伝達物質</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7795,7 +7922,6 @@
           <t>前庭平衡系の構造と機能</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7887,7 +8013,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>網膜</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7979,7 +8109,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>骨格筋弛緩剤（ボツリヌス毒素を含む）</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8071,7 +8205,6 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8163,7 +8296,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>小児期</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8255,7 +8392,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8347,7 +8483,11 @@
           <t>瞳孔反応</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>対光反射</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8439,7 +8579,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8531,7 +8675,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -8623,7 +8771,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8715,7 +8862,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8807,7 +8958,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8899,7 +9049,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -8991,7 +9140,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>4</v>
       </c>
@@ -9084,7 +9237,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9176,7 +9333,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9268,7 +9429,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>3</v>
       </c>
@@ -9360,7 +9520,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>両眼共同運動、両眼離反運動</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9452,7 +9616,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9545,7 +9713,11 @@
           <t>薬物の投与法</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>局所投与</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9637,7 +9809,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>5</v>
       </c>
@@ -9730,7 +9906,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>4</v>
       </c>
@@ -9822,7 +9997,11 @@
           <t>色覚検査</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>アノマロスコープ</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>3</v>
       </c>
@@ -9914,7 +10093,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>角膜内皮細胞検査</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10006,7 +10189,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10098,7 +10285,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10190,7 +10376,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10282,7 +10472,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>3</v>
       </c>
@@ -10374,7 +10563,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>3</v>
       </c>
@@ -10466,7 +10654,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10558,7 +10750,6 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10650,7 +10841,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>3</v>
       </c>
@@ -10742,7 +10932,11 @@
           <t>患者、障害者への検査</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>小児、高齢者、障害者への対応</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -10834,7 +11028,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10926,7 +11119,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11018,7 +11215,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>糖尿病網膜症</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11110,7 +11311,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11202,7 +11407,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>3</v>
       </c>
@@ -11294,7 +11503,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11386,7 +11594,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11478,7 +11685,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11570,7 +11776,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11662,7 +11867,6 @@
           <t>視能障害のリハビリテーション</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>2</v>
       </c>
@@ -11760,7 +11964,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11852,7 +12060,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>4</v>
       </c>
@@ -11944,7 +12151,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12036,7 +12242,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12128,7 +12338,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>1</v>
       </c>
@@ -12220,7 +12434,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>4</v>
       </c>
@@ -12312,7 +12525,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12404,7 +12621,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12496,7 +12712,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12588,7 +12808,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12680,7 +12899,11 @@
           <t>ロービジョン</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>評価</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>2</v>
       </c>
@@ -12772,7 +12995,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>複視</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>4</v>
       </c>
@@ -12865,7 +13092,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>微小斜視弱視</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>3</v>
       </c>
@@ -12957,7 +13188,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>4</v>
       </c>
@@ -13049,7 +13284,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>4</v>
       </c>
@@ -13141,7 +13375,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13233,7 +13471,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13325,7 +13567,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>A-V型斜視</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13417,7 +13663,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>4</v>
       </c>
@@ -13509,7 +13759,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13607,7 +13856,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>5</v>
       </c>
@@ -13700,7 +13953,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13798,7 +14050,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>弱化術</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13896,7 +14152,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>3</v>
       </c>
@@ -13989,7 +14249,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14082,7 +14341,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14180,7 +14438,6 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>4</v>
       </c>
@@ -14278,7 +14535,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14371,7 +14627,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ペナリゼーション</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2015.xlsx
+++ b/CO国試data/CO_questions_2015.xlsx
@@ -603,10 +603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -699,10 +697,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,10 +882,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,10 +971,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1068,10 +1060,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1164,10 +1154,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1260,10 +1248,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1442,10 +1428,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1624,10 +1608,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1720,10 +1702,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1816,10 +1796,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1912,10 +1890,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2008,10 +1984,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2104,10 +2078,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2200,10 +2172,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2296,10 +2266,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2392,10 +2360,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2488,10 +2454,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2590,10 +2554,8 @@
           <t>2015_co_15_am022.jpg</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2777,10 +2739,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2874,10 +2834,8 @@
           <t>2015_co_15_am025.jpg</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2970,10 +2928,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3061,10 +3017,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3253,10 +3207,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3451,10 +3403,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3542,10 +3492,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3638,10 +3586,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3729,10 +3675,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3916,10 +3860,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4103,10 +4045,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4194,10 +4134,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4482,10 +4420,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4573,10 +4509,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4664,10 +4598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4755,10 +4687,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4846,10 +4776,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4937,10 +4865,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5033,10 +4959,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5124,10 +5048,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5215,10 +5137,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5306,10 +5226,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5397,10 +5315,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5584,10 +5500,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5680,10 +5594,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5771,10 +5683,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5862,10 +5772,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6060,10 +5968,8 @@
           <t>2015_co_15_am059.jpg</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6151,10 +6057,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6429,10 +6333,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6525,10 +6427,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6621,10 +6521,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6718,10 +6616,8 @@
           <t>2015_co_15_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6820,10 +6716,8 @@
           <t>2015_co_15_am067.jpg</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6912,10 +6806,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7009,10 +6901,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7111,10 +7001,8 @@
           <t>2015_co_15_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S71" t="b">
+        <v>0</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7305,10 +7193,8 @@
           <t>2015_co_15_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7402,10 +7288,8 @@
           <t>2015_co_15_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7499,10 +7383,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7596,10 +7478,8 @@
           <t>2015_co_15_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7783,10 +7663,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7879,10 +7757,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7970,10 +7846,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8066,10 +7940,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8162,10 +8034,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8253,10 +8123,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8349,10 +8217,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8440,10 +8306,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8536,10 +8400,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8632,10 +8494,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8728,10 +8588,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8819,10 +8677,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8915,10 +8771,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9006,10 +8860,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9097,10 +8949,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9386,10 +9236,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9477,10 +9325,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9573,10 +9419,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9670,10 +9514,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9766,10 +9608,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9863,10 +9703,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9954,10 +9792,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10050,10 +9886,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10146,10 +9980,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10333,10 +10165,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10429,10 +10259,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10520,10 +10348,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10611,10 +10437,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10707,10 +10531,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10889,10 +10711,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11076,10 +10896,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11551,10 +11369,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11642,10 +11458,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11824,10 +11638,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12017,10 +11829,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12108,10 +11918,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12199,10 +12007,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12391,10 +12197,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12482,10 +12286,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12578,10 +12380,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12765,10 +12565,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12952,10 +12750,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13145,10 +12941,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13428,10 +13222,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13620,10 +13412,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13813,10 +13603,8 @@
           <t>2015_co_15_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13910,10 +13698,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14109,10 +13895,8 @@
           <t>2015_co_15_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14206,10 +13990,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14298,10 +14080,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14395,10 +14175,8 @@
           <t>2015_co_15_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14492,10 +14270,8 @@
           <t>2015_co_15_pm073.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14584,10 +14360,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2015.xlsx
+++ b/CO国試data/CO_questions_2015.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -791,10 +791,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S4" t="b">
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1324,7 +1322,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1337,10 +1335,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S10" t="b">
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1504,7 +1500,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1517,10 +1513,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S12" t="b">
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2635,7 +2629,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2648,10 +2642,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S24" t="b">
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3098,7 +3090,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3111,10 +3103,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S29" t="b">
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3289,7 +3279,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3307,10 +3297,8 @@
           <t>2015_co_15_am030.jpg</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S31" t="b">
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3751,7 +3739,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3764,10 +3752,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S36" t="b">
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3941,7 +3927,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3954,10 +3940,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S38" t="b">
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4215,7 +4199,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4228,10 +4212,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S41" t="b">
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4311,7 +4293,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4324,10 +4306,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S42" t="b">
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5396,7 +5376,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5409,10 +5389,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S54" t="b">
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5853,7 +5831,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5866,10 +5844,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6133,7 +6109,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6146,10 +6122,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S62" t="b">
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6224,7 +6198,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6237,10 +6211,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S63" t="b">
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7078,7 +7050,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7096,10 +7068,8 @@
           <t>2015_co_15_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S72" t="b">
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7559,7 +7529,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7572,10 +7542,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S77" t="b">
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9031,7 +8999,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -9044,10 +9012,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S93" t="b">
+        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9127,7 +9093,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -9140,10 +9106,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S94" t="b">
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,7 +10025,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10074,10 +10038,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S104" t="b">
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10607,7 +10569,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -10620,10 +10582,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S110" t="b">
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10792,7 +10752,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10805,10 +10765,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S112" t="b">
+        <v>1</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10977,7 +10935,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -10990,10 +10948,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S114" t="b">
+        <v>1</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11073,7 +11029,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -11086,10 +11042,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S115" t="b">
+        <v>1</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11169,7 +11123,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11182,10 +11136,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S116" t="b">
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11265,7 +11217,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -11278,10 +11230,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S117" t="b">
+        <v>1</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11534,7 +11484,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -11547,10 +11497,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S120" t="b">
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11715,7 +11663,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -11733,10 +11681,8 @@
           <t>2015_co_15_pm046.jpg</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S122" t="b">
+        <v>1</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12088,7 +12034,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12101,10 +12047,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12456,7 +12400,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -12469,10 +12413,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S130" t="b">
+        <v>1</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12641,7 +12583,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -12654,10 +12596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S132" t="b">
+        <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12832,7 +12772,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -12845,10 +12785,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S134" t="b">
+        <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13022,7 +12960,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -13035,10 +12973,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13113,7 +13049,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -13126,10 +13062,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S137" t="b">
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13303,7 +13237,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -13316,10 +13250,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S139" t="b">
+        <v>1</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13493,7 +13425,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -13506,10 +13438,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S141" t="b">
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13775,7 +13705,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -13793,10 +13723,8 @@
           <t>2015_co_15_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S144" t="b">
+        <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14442,7 +14370,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -14455,10 +14383,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S151" t="b">
+        <v>1</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
